--- a/Index/ministerium_aliases.xlsx
+++ b/Index/ministerium_aliases.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>MHKBD</t>
+          <t>MHKBG</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -646,7 +646,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>MBEIM</t>
+          <t>MHKBD</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -864,36 +864,36 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Ministerpräsident</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>STK</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Ministerpräsidentin</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>STK</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Minister Bundes- und Europaangelegenheiten, Internationales sowie Medien und</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>MBEIM</t>
         </is>
@@ -1134,13 +1134,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39B16F14-A05A-4986-91CD-AA989B240CE6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67816E37-E84E-4C80-B3A8-9DCBB0AA8DDD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F9A485C-F543-463D-8E95-4B12B16B9FCC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{794F5F7C-956B-482C-A5C2-15C10782FABE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09017F22-304B-4C39-8EA6-CFC12C568D45}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{357D316B-4B24-428E-B881-5A3D7C41A0FE}"/>
 </file>
--- a/Index/ministerium_aliases.xlsx
+++ b/Index/ministerium_aliases.xlsx
@@ -343,7 +343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.515625" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="51.07" customWidth="1" style="2" min="1" max="1"/>
@@ -896,6 +896,18 @@
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>MBEIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Minister Fianzen</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>FM</t>
         </is>
       </c>
     </row>
@@ -1134,13 +1146,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67816E37-E84E-4C80-B3A8-9DCBB0AA8DDD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8508C11-6965-4206-B6A5-846875617E07}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{794F5F7C-956B-482C-A5C2-15C10782FABE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF14069B-645E-48E8-B64D-BE519202E355}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{357D316B-4B24-428E-B881-5A3D7C41A0FE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5C157D2-ACBB-496B-A0F4-215A47C049B7}"/>
 </file>